--- a/main/ig/ValueSet-fr-vs-edqm-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-edqm-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T10:05:30+00:00</t>
+    <t>2026-03-13T14:11:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-edqm-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-edqm-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T14:11:35+00:00</t>
+    <t>2026-03-13T17:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-edqm-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-edqm-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:00:40+00:00</t>
+    <t>2026-03-13T17:26:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-edqm-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-edqm-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:26:39+00:00</t>
+    <t>2026-03-13T17:26:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-edqm-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-edqm-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:26:16+00:00</t>
+    <t>2026-03-13T22:26:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-edqm-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-edqm-document.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.0-snapsnot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T22:26:12+00:00</t>
+    <t>2026-03-20T08:18:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-edqm-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-edqm-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T08:18:16+00:00</t>
+    <t>2026-03-23T13:14:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-edqm-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-edqm-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T13:14:10+00:00</t>
+    <t>2026-03-27T09:33:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-edqm-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-edqm-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T09:33:49+00:00</t>
+    <t>2026-03-30T15:11:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-edqm-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-edqm-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T15:11:58+00:00</t>
+    <t>2026-03-31T07:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-edqm-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-edqm-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T07:16:03+00:00</t>
+    <t>2026-04-01T07:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-edqm-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-edqm-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T07:43:12+00:00</t>
+    <t>2026-04-02T07:21:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-edqm-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-edqm-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T07:21:27+00:00</t>
+    <t>2026-04-02T12:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-edqm-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-edqm-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T12:41:19+00:00</t>
+    <t>2026-04-07T08:23:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-edqm-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-edqm-document.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T08:23:13+00:00</t>
+    <t>2026-04-15T13:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-edqm-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-edqm-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T13:29:57+00:00</t>
+    <t>2026-04-15T15:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-edqm-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-edqm-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T15:41:19+00:00</t>
+    <t>2026-04-20T15:11:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-edqm-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-edqm-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:11:12+00:00</t>
+    <t>2026-04-23T15:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-edqm-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-edqm-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T15:25:59+00:00</t>
+    <t>2026-05-06T07:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-edqm-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-edqm-document.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:44:21+00:00</t>
+    <t>2026-05-13T14:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>ValueSet basé sur le CodeSystem EDQM fourni par SMT</t>
+    <t>ValueSet basé sur le CodeSystem EDQM fourni par SMT. classe PDF (forme galénique).</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -99,10 +99,16 @@
     <t>BooleanType[null]</t>
   </si>
   <si>
-    <t>Codes</t>
-  </si>
-  <si>
-    <t>All codes</t>
+    <t>Operation</t>
+  </si>
+  <si>
+    <t>concept</t>
+  </si>
+  <si>
+    <t>is-a</t>
+  </si>
+  <si>
+    <t>PDF</t>
   </si>
   <si>
     <t/>
@@ -375,7 +381,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -384,28 +390,40 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s" s="1">
         <v>28</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
         <v>29</v>
       </c>
+      <c r="B2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>31</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/main/ig/ValueSet-fr-vs-edqm-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-edqm-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:53:03+00:00</t>
+    <t>2026-05-15T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-edqm-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-edqm-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-edqm-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-edqm-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-edqm-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-edqm-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-edqm-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-edqm-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-edqm-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-edqm-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-edqm-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-edqm-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-vs-edqm-document.xlsx
+++ b/main/ig/ValueSet-fr-vs-edqm-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
